--- a/measurements/34/Filled_2D_sections/sagittal/week34_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/34/Filled_2D_sections/sagittal/week34_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,97 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +591,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.581796549672815</v>
+        <v>3271.201814058957</v>
       </c>
       <c r="D2" t="n">
-        <v>15.14943846260629</v>
+        <v>295.774750936599</v>
       </c>
       <c r="E2" t="n">
-        <v>13.04392870170314</v>
+        <v>254.6671794142042</v>
       </c>
       <c r="F2" t="n">
         <v>1.161416840666128</v>
@@ -525,24 +610,51 @@
         <v>0.4698887071745597</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6031821646341463</v>
+        <v>1.343005952380952</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7804878048780488</v>
+        <v>15.23809523809524</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6918349847560976</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>5.524819302721087</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15.23809523809524</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11.77641369047619</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.343005952380952</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.597470238095238</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.331845238095238</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>8.45144259369423</v>
+      <c r="AF2" s="2" t="n">
+        <v>3221.513605442177</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +665,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.823616894705532</v>
+        <v>3363.378684807256</v>
       </c>
       <c r="D3" t="n">
-        <v>16.36649933384686</v>
+        <v>319.5364155655815</v>
       </c>
       <c r="E3" t="n">
-        <v>13.01188705607158</v>
+        <v>254.0416044280642</v>
       </c>
       <c r="F3" t="n">
         <v>1.257811358438587</v>
@@ -572,24 +684,54 @@
         <v>0.4139471656663257</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.488095238095238</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.54501488095238</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.131035052910052</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15.54501488095238</v>
+      </c>
+      <c r="N3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.5856516768292683</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.7962080792682927</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.6909298780487805</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>11.43415178571428</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.165550595238095</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.488095238095238</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.454241071428571</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.339099702380952</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>15.59376809204497</v>
+      <c r="AF3" s="2" t="n">
+        <v>304.4497579875446</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +742,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.963414634146343</v>
+        <v>3416.666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>14.36793531150353</v>
+        <v>280.5168322722117</v>
       </c>
       <c r="E4" t="n">
-        <v>13.03801065537988</v>
+        <v>254.5516366050357</v>
       </c>
       <c r="F4" t="n">
         <v>1.102003648507135</v>
@@ -619,24 +761,54 @@
         <v>0.545625454358593</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>0.594702743902439</v>
+        <v>1.329985119047619</v>
       </c>
       <c r="J4" t="n">
-        <v>0.594702743902439</v>
+        <v>11.61086309523809</v>
       </c>
       <c r="K4" t="n">
-        <v>0.594702743902439</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>4.185681216931218</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11.61086309523809</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.149181547619047</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.704241071428571</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.329985119047619</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.077380952380953</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.201140873015873</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>12.57960025333777</v>
+      <c r="AF4" s="2" t="n">
+        <v>245.6017192318326</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +819,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.983343248066628</v>
+        <v>3424.263038548753</v>
       </c>
       <c r="D5" t="n">
-        <v>14.4916198747914</v>
+        <v>282.9316261268797</v>
       </c>
       <c r="E5" t="n">
-        <v>12.96555789505563</v>
+        <v>253.1370827129909</v>
       </c>
       <c r="F5" t="n">
         <v>1.117701219807728</v>
@@ -666,23 +838,53 @@
         <v>0.5375439655064062</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6078506097560976</v>
+        <v>1.847098214285714</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6078506097560976</v>
+        <v>11.86755952380952</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6078506097560976</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>4.678896949404763</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>11.86755952380952</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7.730654761904762</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.210193452380952</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.847098214285714</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.980654761904762</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.524553571428571</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AF5" s="2" t="n">
         <v>1.24111708511174</v>
       </c>
     </row>
@@ -694,42 +896,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.974419988102321</v>
+        <v>3420.861678004535</v>
       </c>
       <c r="D6" t="n">
-        <v>15.26720499410862</v>
+        <v>298.0740022659302</v>
       </c>
       <c r="E6" t="n">
-        <v>12.96555792122352</v>
+        <v>253.1370832238878</v>
       </c>
       <c r="F6" t="n">
         <v>1.177520094921445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4838348870472824</v>
+        <v>0.4838348870472823</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5943216463414634</v>
+        <v>1.441592261904762</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5943216463414634</v>
+        <v>11.60342261904762</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5943216463414634</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>4.956597222222221</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.111607142857142</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11.60342261904762</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7.785063244047618</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.09970238095238</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.693824404761904</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
         <v>0.441213412561604</v>
       </c>
     </row>
@@ -741,43 +973,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.944973230220107</v>
+        <v>3409.637188208616</v>
       </c>
       <c r="D7" t="n">
-        <v>15.35047847468679</v>
+        <v>299.6998178391229</v>
       </c>
       <c r="E7" t="n">
-        <v>12.94290100946659</v>
+        <v>252.6947339943477</v>
       </c>
       <c r="F7" t="n">
-        <v>1.186015288493613</v>
+        <v>1.186015288493612</v>
       </c>
       <c r="G7" t="n">
         <v>0.4770293222042568</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5955602134146342</v>
+        <v>1.376488095238095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5955602134146342</v>
+        <v>11.62760416666667</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5955602134146342</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>5.3895916005291</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.111607142857142</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11.62760416666667</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8.512834821428571</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.376488095238095</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.790922619047619</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.890997023809523</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.25</v>
+      <c r="AF7" s="2" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1050,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.91017251635931</v>
+        <v>3396.371882086168</v>
       </c>
       <c r="D8" t="n">
-        <v>15.13760235832959</v>
+        <v>295.5436650911967</v>
       </c>
       <c r="E8" t="n">
-        <v>12.88228440575483</v>
+        <v>251.5112669694991</v>
       </c>
       <c r="F8" t="n">
-        <v>1.175071274747455</v>
+        <v>1.175071274747454</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4886318719321776</v>
+        <v>0.4886318719321777</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5043826219512195</v>
+        <v>1.391369047619047</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5813643292682927</v>
+        <v>11.35044642857143</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5428734756097562</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>5.23478835978836</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.014880952380952</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11.35044642857143</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8.280784970238095</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.391369047619047</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.947172619047619</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.797991071428571</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5813976753048781</v>
+      <c r="AF8" s="2" t="n">
+        <v>1.621837797619047</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1127,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.844735276621059</v>
+        <v>3371.428571428571</v>
       </c>
       <c r="D9" t="n">
-        <v>15.44212141560345</v>
+        <v>301.4890371617817</v>
       </c>
       <c r="E9" t="n">
-        <v>12.87983307024328</v>
+        <v>251.4634075618926</v>
       </c>
       <c r="F9" t="n">
         <v>1.19893800885354</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4661017970506275</v>
+        <v>0.4661017970506277</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5563071646341463</v>
+        <v>2.509300595238095</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5563071646341463</v>
+        <v>10.86123511904762</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5563071646341463</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>5.583612351190476</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.800967261904762</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10.86123511904762</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.927362351190477</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.509300595238095</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.986235119047619</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.239862351190476</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.6101753048780487</v>
+      <c r="AF9" s="2" t="n">
+        <v>11.91294642857143</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1204,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.765913146936349</v>
+        <v>3341.383219954648</v>
       </c>
       <c r="D10" t="n">
-        <v>14.91635680489424</v>
+        <v>291.2241090479351</v>
       </c>
       <c r="E10" t="n">
-        <v>12.64675139217842</v>
+        <v>246.9127652758644</v>
       </c>
       <c r="F10" t="n">
         <v>1.179461534613505</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4950869748939164</v>
+        <v>0.4950869748939165</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>0.54296875</v>
+        <v>1.326264880952381</v>
       </c>
       <c r="J10" t="n">
-        <v>0.54296875</v>
+        <v>10.60081845238095</v>
       </c>
       <c r="K10" t="n">
-        <v>0.54296875</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>4.930348875661376</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10.60081845238095</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7.606956845238095</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.326264880952381</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.461681547619047</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.7890625</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.5957864900914634</v>
+      <c r="AF10" s="2" t="n">
+        <v>5.247948951883103</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1281,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.721891731112434</v>
+        <v>3324.603174603174</v>
       </c>
       <c r="D11" t="n">
-        <v>14.83553463365974</v>
+        <v>289.6461523714519</v>
       </c>
       <c r="E11" t="n">
-        <v>12.62654583628585</v>
+        <v>246.5182758512951</v>
       </c>
       <c r="F11" t="n">
         <v>1.174947988627717</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4979825809793059</v>
+        <v>0.497982580979306</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5493521341463414</v>
+        <v>2.490699404761905</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5493521341463414</v>
+        <v>10.72544642857143</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5493521341463414</v>
+        <v>5.407366071428571</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10.72544642857143</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9.380580357142856</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.595238095238095</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.490699404761905</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.155505952380953</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.511532738095238</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1358,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.558001189767996</v>
+        <v>3262.131519274376</v>
       </c>
       <c r="D12" t="n">
-        <v>15.62540721893311</v>
+        <v>305.0674742744083</v>
       </c>
       <c r="E12" t="n">
-        <v>12.53490293316725</v>
+        <v>244.7290572665986</v>
       </c>
       <c r="F12" t="n">
         <v>1.246551912068534</v>
@@ -987,16 +1377,51 @@
         <v>0.4404732285471353</v>
       </c>
       <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.36086309523809</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.391136532738095</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.973958333333333</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10.36086309523809</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7.454427083333333</v>
+      </c>
+      <c r="U12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.5046684451219512</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5306783536585366</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.5176733993902438</v>
+      <c r="V12" t="n">
+        <v>3.941592261904762</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>13.8538566468254</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1432,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.385782272456872</v>
+        <v>3196.485260770975</v>
       </c>
       <c r="D13" t="n">
-        <v>16.95186516424505</v>
+        <v>330.9649865400223</v>
       </c>
       <c r="E13" t="n">
-        <v>12.44571137428284</v>
+        <v>242.9876982598078</v>
       </c>
       <c r="F13" t="n">
         <v>1.36206478315683</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3667063814224074</v>
+        <v>0.3667063814224075</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5473513719512195</v>
+        <v>1.506696428571428</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5473513719512195</v>
+        <v>10.68638392857143</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5473513719512195</v>
+        <v>6.144717261904761</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.634300595238095</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10.68638392857143</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.612041170634919</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.506696428571428</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.619791666666667</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.443731398809524</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>4.35</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1509,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.226353361094587</v>
+        <v>3135.714285714285</v>
       </c>
       <c r="D14" t="n">
-        <v>17.32537025358619</v>
+        <v>338.2572287604922</v>
       </c>
       <c r="E14" t="n">
-        <v>12.46591690691506</v>
+        <v>243.3821872302464</v>
       </c>
       <c r="F14" t="n">
         <v>1.389819167170568</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3443913030055578</v>
+        <v>0.3443913030055579</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5571646341463414</v>
+        <v>1.497395833333333</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5571646341463414</v>
+        <v>10.87797619047619</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5571646341463414</v>
+        <v>6.03422619047619</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4.110863095238095</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10.87797619047619</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.462332589285714</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.407738095238095</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.772693452380952</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.497395833333333</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>10.58221726190476</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1586,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.006841165972636</v>
+        <v>3052.040816326531</v>
       </c>
       <c r="D15" t="n">
-        <v>17.17412609879564</v>
+        <v>335.3043666907719</v>
       </c>
       <c r="E15" t="n">
-        <v>12.53000026505168</v>
+        <v>244.6333385081518</v>
       </c>
       <c r="F15" t="n">
-        <v>1.370640521588592</v>
+        <v>1.370640521588593</v>
       </c>
       <c r="G15" t="n">
         <v>0.3411314676634497</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5461128048780488</v>
+        <v>2.144717261904762</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5461128048780488</v>
+        <v>10.66220238095238</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5461128048780488</v>
+        <v>6.670758928571426</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6.83407738095238</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10.66220238095238</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8.440954506802719</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.193824404761905</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.282366071428571</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.144717261904762</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>6.79501488095238</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1663,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.969660916121357</v>
+        <v>3037.868480725623</v>
       </c>
       <c r="D16" t="n">
-        <v>16.45670627675405</v>
+        <v>321.2975987366268</v>
       </c>
       <c r="E16" t="n">
-        <v>12.39447953352114</v>
+        <v>241.9874575592223</v>
       </c>
       <c r="F16" t="n">
         <v>1.327744842552407</v>
@@ -1143,16 +1682,54 @@
         <v>0.369797416143227</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>0.553734756097561</v>
+        <v>1.569940476190476</v>
       </c>
       <c r="J16" t="n">
-        <v>0.553734756097561</v>
+        <v>10.8110119047619</v>
       </c>
       <c r="K16" t="n">
-        <v>0.553734756097561</v>
+        <v>5.63290550595238</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.954241071428571</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10.8110119047619</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7.65704719387755</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.569940476190476</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.6328125</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.799107142857143</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>4.858630952380952</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1740,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.955383700178466</v>
+        <v>3032.426303854875</v>
       </c>
       <c r="D17" t="n">
-        <v>15.74173777277877</v>
+        <v>307.3386898494902</v>
       </c>
       <c r="E17" t="n">
-        <v>12.17323399462351</v>
+        <v>237.6679017997923</v>
       </c>
       <c r="F17" t="n">
         <v>1.293143447314932</v>
@@ -1182,16 +1759,54 @@
         <v>0.4034276384251278</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5038109756097561</v>
+        <v>1.22953869047619</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5885099085365854</v>
+        <v>11.48995535714286</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5461604420731707</v>
+        <v>5.102461557539681</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.702380952380953</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11.48995535714286</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6.906622023809523</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22953869047619</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.121279761904762</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.576636904761905</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>5.040922619047619</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1817,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.956870910172516</v>
+        <v>3032.993197278911</v>
       </c>
       <c r="D18" t="n">
-        <v>15.60968374915239</v>
+        <v>304.7604922453562</v>
       </c>
       <c r="E18" t="n">
-        <v>12.11853543432747</v>
+        <v>236.5999775273459</v>
       </c>
       <c r="F18" t="n">
         <v>1.288083352459881</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4103590044386529</v>
+        <v>0.410359004438653</v>
       </c>
       <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.238839285714286</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12.63206845238095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.809337797619047</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.6470083841463414</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.6470083841463414</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.6470083841463414</v>
+      <c r="M18" t="n">
+        <v>12.63206845238095</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.76376488095238</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9.640997023809524</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.098400297619047</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.238839285714286</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.857886904761905</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.955197704081633</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>10.7298820970696</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +1897,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.906900654372397</v>
+        <v>3013.945578231292</v>
       </c>
       <c r="D19" t="n">
-        <v>15.45150617273842</v>
+        <v>301.6722633725121</v>
       </c>
       <c r="E19" t="n">
-        <v>12.07567301610621</v>
+        <v>235.7631398382641</v>
       </c>
       <c r="F19" t="n">
         <v>1.279556522616141</v>
@@ -1260,16 +1916,57 @@
         <v>0.4161735803531296</v>
       </c>
       <c r="H19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.212797619047619</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12.8031994047619</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.332074175824176</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6557736280487805</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.6557736280487805</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.6557736280487805</v>
+      <c r="M19" t="n">
+        <v>12.8031994047619</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8.915550595238095</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5.703125</v>
+      </c>
+      <c r="U19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.212797619047619</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.952752976190476</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.587658110119048</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>7.57291939211582</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +1977,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.82064247471743</v>
+        <v>2981.065759637188</v>
       </c>
       <c r="D20" t="n">
-        <v>15.15882326626196</v>
+        <v>295.9579780555907</v>
       </c>
       <c r="E20" t="n">
-        <v>12.05301611307191</v>
+        <v>235.3207907790229</v>
       </c>
       <c r="F20" t="n">
         <v>1.257678835243711</v>
@@ -1299,16 +1996,57 @@
         <v>0.4276823394802957</v>
       </c>
       <c r="H20" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.2109375</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12.81808035714286</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.136332417582417</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6565358231707318</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.6565358231707318</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.6565358231707318</v>
+      <c r="M20" t="n">
+        <v>12.81808035714286</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.753720238095237</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.78422619047619</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.620535714285714</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2109375</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.824404761904762</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.532862103174603</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>5.15</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2057,76 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.728138013087448</v>
+        <v>2945.804988662131</v>
       </c>
       <c r="D21" t="n">
-        <v>15.05534420362333</v>
+        <v>293.9376725469317</v>
       </c>
       <c r="E21" t="n">
-        <v>11.79727755232555</v>
+        <v>230.3277998311179</v>
       </c>
       <c r="F21" t="n">
-        <v>1.276171060386345</v>
+        <v>1.276171060386346</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4284531649396439</v>
+        <v>0.428453164939644</v>
       </c>
       <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14.08668154761905</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.682291666666667</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.7215129573170732</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.7215129573170732</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7215129573170732</v>
+      <c r="M21" t="n">
+        <v>14.08668154761905</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7.907366071428571</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.559895833333333</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.162946428571428</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.655133928571428</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.517671130952381</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>3.514384920634921</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2136,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>2.171999007936508</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2158,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>1.821056547619047</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2175,70 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>1.549041491596638</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>3.77735469187675</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>2.690163174644858</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/34/Filled_2D_sections/sagittal/week34_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/34/Filled_2D_sections/sagittal/week34_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2244,4 +2450,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week34_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3221.513605442177</v>
+      </c>
+      <c r="D10" t="n">
+        <v>174.0018243902538</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2945.804988662131</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3424.263038548753</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>304.4497579875447</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.48771606099911</v>
+      </c>
+      <c r="E11" t="n">
+        <v>280.5168322722117</v>
+      </c>
+      <c r="F11" t="n">
+        <v>338.2572287604922</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.24111708511174</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.08321204164439162</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.102003648507135</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.389819167170568</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.441213412561604</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05948695313379117</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3411314676634497</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.545625454358593</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0165.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0167.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0169.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0171.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0173.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0177.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0178.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0179.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0180.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0181.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0182.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0183.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>13</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>13</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0185.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.794729124848357</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4701623459816272</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.871531880291482</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.631111987507134</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13.8538566468254</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.303826647948155</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.63206845238095</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15.54501488095238</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>87</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.631341509304869</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.19337263041137</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.110863095238095</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.86755952380952</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>103</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.665478357605178</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7759021020157351</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.2109375</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.155505952380953</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>